--- a/docs/PRAP_Development_Plan_v2.73.xlsx
+++ b/docs/PRAP_Development_Plan_v2.73.xlsx
@@ -7823,7 +7823,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>R-64, REQ-PRJ-17: THIRTEEN HIGHLIGHT COLOURS. Asked for from the field: 'at least 12 distinctive colours' for highlighting - five ran out as soon as a team gave each kind of milestone or period its own. The palette is now red, orange, yellow, lime, green, teal, cyan, blue, navy, purple, magenta, pink and brown, for milestones and periods alike, each defined for the light and the dark theme and no two closer than a set distance in either (yellow was moved away from orange to get there - the two of the original five that were nearest). A band's label is dark on the four pale ones. The template's Lists offer all thirteen; a workbook made before them, whose Lists hold five, is offered the other eight as well, so the new colours can be chosen without editing its Lists. The value chooser shows each colour as a swatch beside its name. THE COLOUR WORD IS NOW READ AS A WORD: 'Highlight (Green) - redo' used to be red, because the letters r-e-d appear in it; now a colour word must stand on its own and the first one named wins - Korean text beside it does not hide it. Mirrored in the Python reference. No figure moves; no schema change. Template v1.21, examples v1.23 and v1.15. tools/test_highlight.py gains ten checks. Python edition 1.36.</t>
+          <t>R-64, REQ-PRJ-17: THIRTEEN HIGHLIGHT COLOURS. Asked for from the field: 'at least 12 distinctive colours' for highlighting - five ran out as soon as a team gave each kind of milestone or period its own. The palette is now red, orange, yellow, lime, green, teal, cyan, blue, navy, purple, magenta, pink and brown, for milestones and periods alike, each defined for the light and the dark theme and no two closer than a set distance in either (yellow was moved away from orange to get there - the two of the original five that were nearest). A band's label is dark on the four pale ones. The template's Lists offer all thirteen; a workbook made before them, whose Lists hold five, is offered the other eight as well, so the new colours can be chosen without editing its Lists. The value chooser shows each colour as a swatch beside its name. THE COLOUR WORD IS NOW READ AS A WORD: 'Highlight (Green) - redo' used to be red, because the letters r-e-d appear in it; now a colour word must stand on its own and the first one named wins - Korean text beside it does not hide it. Mirrored in the Python reference. No figure moves; no schema change. Template v1.21, examples v1.23 and v1.15. tools/test_highlight.py gains ten checks. Python edition 1.36. Also asked for: the Monthly estimation panel on Source data (project) is titled by the project's NAME, with its identifier quieter beside it, instead of the identifier alone (an assignment's panel keeps its id, with the line under it).</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
